--- a/tools.xlsx
+++ b/tools.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:T62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,7 +961,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Miilwaukee</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Miilwaukee</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Miilwaukee</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Miilwaukee</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Miilwaukee</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Miilwaukee</t>
+          <t>Milwaukee</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3404,6 +3404,846 @@
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>966F68B1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Milwaukee</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>7-1/4 Inch Miter Saw</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Miter Saw</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>18v</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Milwaukee M18</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2023-10-17</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>515</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>photos/966F68B1.png</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>F42B2F90</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>DeWalt</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Cordless Oscillating Tool</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Oscillating Tool</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>18v</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DeWalt 20V MAX</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>130</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>photos/F42B2F90.png</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>6EF9CA1E</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Wen</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Scroll Saw</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Scroll Saw</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Corded electric</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>110v</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>130</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>photos/6EF9CA1E.png</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>C6DB5D4B</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Bucktool</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2x42" Belt Sander And Grinder Combo</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sander</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Corded electric</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>160</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Temu</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>photos/C6DB5D4B.png</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DF310590</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Vevor</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>8-Inch Wet Sharpening System</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Grinder</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Corded electric</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>110v</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>150</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Best Buy</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>photos/DF310590.png</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3606D97C</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Wen</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>6-Amp Electric Hand Planer</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Planer</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Corded electric</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>110v</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2019-01-09</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>45</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>photos/3606D97C.png</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>D1645CB3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ego</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Backpack Blower</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Blower</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>56V</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Ego 56V</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>300</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Acme Tools</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>photos/D1645CB3.png</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C11A25D6</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ego</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Cordless Blower</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Blower</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>56V</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Ego 56V</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="n">
+        <v>180</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Ace Hardware</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>photos/C11A25D6.png</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>E7DC530C</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ego</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>24" Snow Blower</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Snow Blower</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>56V</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Ego 56V</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>2150</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>photos/E7DC530C.png</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BFE7AF30</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ego</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>21" Lawn Mower</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Lawn Mower</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>56V</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ego 56V</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2023-06-05</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>542</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>photos/BFE7AF30.png</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>7F18DF17</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Ego</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>String Trimmer</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Trimmer</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>56V</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ego 56V</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2023-05-15</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>180</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Ace Hardware</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>photos/7F18DF17.png</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>298A50FE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Worx</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>String Trimmer</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Trimmer</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>20V</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Worx 20V</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2018-05-02</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>162</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>photos/298A50FE.png</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>B91FA002</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ryobi</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Hedge Trimmer</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Trimmer</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>18v</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Ryobi ONE+ 18V</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>100</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>photos/B91FA002.png</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3568,7 +4408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3615,7 +4455,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>California Air Tools</t>
+          <t>Bucktool</t>
         </is>
       </c>
     </row>
@@ -3627,7 +4467,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Carbide 3D</t>
+          <t>California Air Tools</t>
         </is>
       </c>
     </row>
@@ -3639,7 +4479,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Craftsman</t>
+          <t>Carbide 3D</t>
         </is>
       </c>
     </row>
@@ -3651,7 +4491,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DeWalt</t>
+          <t>Craftsman</t>
         </is>
       </c>
     </row>
@@ -3663,7 +4503,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Festool</t>
+          <t>DeWalt</t>
         </is>
       </c>
     </row>
@@ -3675,7 +4515,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Glowforge</t>
+          <t>Ego</t>
         </is>
       </c>
     </row>
@@ -3687,7 +4527,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Makita</t>
+          <t>Festool</t>
         </is>
       </c>
     </row>
@@ -3699,7 +4539,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meite</t>
+          <t>Glowforge</t>
         </is>
       </c>
     </row>
@@ -3711,7 +4551,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Metabo HPT</t>
+          <t>Makita</t>
         </is>
       </c>
     </row>
@@ -3723,7 +4563,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Meite</t>
         </is>
       </c>
     </row>
@@ -3735,7 +4575,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Metabo HPT</t>
         </is>
       </c>
     </row>
@@ -3747,7 +4587,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ridgid</t>
+          <t>Milwaukee</t>
         </is>
       </c>
     </row>
@@ -3759,7 +4599,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ryobi</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -3771,7 +4611,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sawstop</t>
+          <t>Ridgid</t>
         </is>
       </c>
     </row>
@@ -3783,7 +4623,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shaper Tools</t>
+          <t>Ryobi</t>
         </is>
       </c>
     </row>
@@ -3795,7 +4635,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wen</t>
+          <t>Sawstop</t>
         </is>
       </c>
     </row>
@@ -3807,55 +4647,55 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>XTOOL</t>
+          <t>Shaper Tools</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Make / Brand</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3d Printer</t>
+          <t>Vevor</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Make / Brand</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Air Compressor</t>
+          <t>Wen</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Make / Brand</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Band Saw</t>
+          <t>Worx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Make / Brand</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Circular Saw</t>
+          <t>XTOOL</t>
         </is>
       </c>
     </row>
@@ -3867,7 +4707,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>3d Printer</t>
         </is>
       </c>
     </row>
@@ -3879,7 +4719,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Drill</t>
+          <t>Air Compressor</t>
         </is>
       </c>
     </row>
@@ -3891,7 +4731,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grinder</t>
+          <t>Band Saw</t>
         </is>
       </c>
     </row>
@@ -3903,7 +4743,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hammer Drill</t>
+          <t>Blower</t>
         </is>
       </c>
     </row>
@@ -3915,7 +4755,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Impact Driver</t>
+          <t>Circular Saw</t>
         </is>
       </c>
     </row>
@@ -3927,7 +4767,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Jigsaw</t>
+          <t>CNC</t>
         </is>
       </c>
     </row>
@@ -3939,7 +4779,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Laser</t>
+          <t>Drill</t>
         </is>
       </c>
     </row>
@@ -3951,7 +4791,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Miter Saw</t>
+          <t>Grinder</t>
         </is>
       </c>
     </row>
@@ -3963,7 +4803,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nail Gun</t>
+          <t>Hammer Drill</t>
         </is>
       </c>
     </row>
@@ -3975,7 +4815,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Oscillating Tool</t>
+          <t>Impact Driver</t>
         </is>
       </c>
     </row>
@@ -3987,7 +4827,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Planer</t>
+          <t>Jigsaw</t>
         </is>
       </c>
     </row>
@@ -3999,7 +4839,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ratchet</t>
+          <t>Laser</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4851,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Lawn Mower</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4863,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sander</t>
+          <t>Miter Saw</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4875,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Shop Vac</t>
+          <t>Nail Gun</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4887,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Table Saw</t>
+          <t>Oscillating Tool</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4899,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Track Saw</t>
+          <t>Planer</t>
         </is>
       </c>
     </row>
@@ -4071,115 +4911,115 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Ratchet</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>Router</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18V</t>
+          <t>Sander</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20V</t>
+          <t>Scroll Saw</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>24V</t>
+          <t>Shop Vac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>36V</t>
+          <t>Snow Blower</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>40V</t>
+          <t>Table Saw</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>60V</t>
+          <t>Track Saw</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>120V</t>
+          <t>Trimmer</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>120V / 240V</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -4191,7 +5031,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Corded / N/A</t>
+          <t>12V</t>
         </is>
       </c>
     </row>
@@ -4203,122 +5043,122 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>18V</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DeWalt 20V MAX</t>
+          <t>20V</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Milwaukee M18</t>
+          <t>24V</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Milwaukee M12</t>
+          <t>36V</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Makita LXT 18V</t>
+          <t>40V</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Makita XGT 40V</t>
+          <t>56V</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bosch 18V</t>
+          <t>60V</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ryobi ONE+ 18V</t>
+          <t>120V</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ridgid 18V</t>
+          <t>120V / 240V</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Craftsman V20</t>
+          <t>Corded / N/A</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4330,106 +5170,286 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>DeWalt 20V MAX</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lowe’s</t>
+          <t>Ego 56V</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Milwaukee M18</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ace Hardware</t>
+          <t>Milwaukee M12</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Harbor Freight</t>
+          <t>Makita LXT 18V</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Northern Tool</t>
+          <t>Makita XGT 40V</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Bosch 18V</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Ryobi ONE+ 18V</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>Battery platform</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Ridgid 18V</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Battery platform</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Craftsman V20</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Battery platform</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Worx 20V</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Battery platform</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Acme Tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Best Buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Lowe’s</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Ace Hardware</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Harbor Freight</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Northern Tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Grainger</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Temu</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
         <is>
           <t>Other</t>
         </is>

--- a/tools.xlsx
+++ b/tools.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T62"/>
+  <dimension ref="A1:T66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4244,6 +4244,258 @@
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>874BCCF5</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ridgid</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>4.5 Gal Shop Vacuum</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Shop Vac</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Corded electric</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>110v</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>80</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>photos/874BCCF5.png</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0C5689DD</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Milwaukee</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>M12 Crown Stapler</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Stapler</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Corded electric</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>12v</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Milwaukee M12</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>100</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>photos/0C5689DD.png</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>F096BA4A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NeoTamarix</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Thermal Imaging Camera</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>267</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>photos/F096BA4A.png</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FC79C593</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Depstech</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Endoscope Camera</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>134</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>photos/FC79C593.png</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4408,7 +4660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4503,7 +4755,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DeWalt</t>
+          <t>Depstech</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4767,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ego</t>
+          <t>DeWalt</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4779,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Festool</t>
+          <t>Ego</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4791,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Glowforge</t>
+          <t>Festool</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4803,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Makita</t>
+          <t>Glowforge</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4815,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Meite</t>
+          <t>Makita</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4827,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Metabo HPT</t>
+          <t>Meite</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4839,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Milwaukee</t>
+          <t>Metabo HPT</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4851,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Milwaukee</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4863,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ridgid</t>
+          <t>NeoTamarix</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4875,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ryobi</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4887,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sawstop</t>
+          <t>Ridgid</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4899,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Shaper Tools</t>
+          <t>Ryobi</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4911,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vevor</t>
+          <t>Sawstop</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4923,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wen</t>
+          <t>Shaper Tools</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4935,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Worx</t>
+          <t>Vevor</t>
         </is>
       </c>
     </row>
@@ -4695,31 +4947,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>XTOOL</t>
+          <t>Wen</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Make / Brand</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3d Printer</t>
+          <t>Worx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Make / Brand</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Air Compressor</t>
+          <t>XTOOL</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4983,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Band Saw</t>
+          <t>3d Printer</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4995,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blower</t>
+          <t>Air Compressor</t>
         </is>
       </c>
     </row>
@@ -4755,7 +5007,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Circular Saw</t>
+          <t>Band Saw</t>
         </is>
       </c>
     </row>
@@ -4767,7 +5019,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>Blower</t>
         </is>
       </c>
     </row>
@@ -4779,7 +5031,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Drill</t>
+          <t>Camera</t>
         </is>
       </c>
     </row>
@@ -4791,7 +5043,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grinder</t>
+          <t>Circular Saw</t>
         </is>
       </c>
     </row>
@@ -4803,7 +5055,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hammer Drill</t>
+          <t>CNC</t>
         </is>
       </c>
     </row>
@@ -4815,7 +5067,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Impact Driver</t>
+          <t>Drill</t>
         </is>
       </c>
     </row>
@@ -4827,7 +5079,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Jigsaw</t>
+          <t>Grinder</t>
         </is>
       </c>
     </row>
@@ -4839,7 +5091,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Laser</t>
+          <t>Hammer Drill</t>
         </is>
       </c>
     </row>
@@ -4851,7 +5103,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lawn Mower</t>
+          <t>Impact Driver</t>
         </is>
       </c>
     </row>
@@ -4863,7 +5115,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Miter Saw</t>
+          <t>Jigsaw</t>
         </is>
       </c>
     </row>
@@ -4875,7 +5127,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nail Gun</t>
+          <t>Laser</t>
         </is>
       </c>
     </row>
@@ -4887,7 +5139,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Oscillating Tool</t>
+          <t>Lawn Mower</t>
         </is>
       </c>
     </row>
@@ -4899,7 +5151,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Planer</t>
+          <t>Miter Saw</t>
         </is>
       </c>
     </row>
@@ -4911,7 +5163,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ratchet</t>
+          <t>Nail Gun</t>
         </is>
       </c>
     </row>
@@ -4923,7 +5175,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Oscillating Tool</t>
         </is>
       </c>
     </row>
@@ -4935,7 +5187,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sander</t>
+          <t>Planer</t>
         </is>
       </c>
     </row>
@@ -4947,7 +5199,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Scroll Saw</t>
+          <t>Ratchet</t>
         </is>
       </c>
     </row>
@@ -4959,7 +5211,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shop Vac</t>
+          <t>Router</t>
         </is>
       </c>
     </row>
@@ -4971,7 +5223,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Snow Blower</t>
+          <t>Sander</t>
         </is>
       </c>
     </row>
@@ -4983,7 +5235,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Table Saw</t>
+          <t>Scroll Saw</t>
         </is>
       </c>
     </row>
@@ -4995,7 +5247,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Track Saw</t>
+          <t>Shop Vac</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5259,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Trimmer</t>
+          <t>Snow Blower</t>
         </is>
       </c>
     </row>
@@ -5019,55 +5271,55 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Stapler</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>Table Saw</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>18V</t>
+          <t>Track Saw</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20V</t>
+          <t>Trimmer</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>24V</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5331,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>36V</t>
+          <t>12V</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5343,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>40V</t>
+          <t>18V</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5355,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>56V</t>
+          <t>20V</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5367,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>60V</t>
+          <t>24V</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5379,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>120V</t>
+          <t>36V</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5391,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>120V / 240V</t>
+          <t>40V</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5403,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Corded / N/A</t>
+          <t>56V</t>
         </is>
       </c>
     </row>
@@ -5163,55 +5415,55 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>60V</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DeWalt 20V MAX</t>
+          <t>120V</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ego 56V</t>
+          <t>120V / 240V</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Milwaukee M18</t>
+          <t>Corded / N/A</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Milwaukee M12</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5475,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Makita LXT 18V</t>
+          <t>DeWalt 20V MAX</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5487,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Makita XGT 40V</t>
+          <t>Ego 56V</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5499,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bosch 18V</t>
+          <t>Milwaukee M18</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5511,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ryobi ONE+ 18V</t>
+          <t>Milwaukee M12</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5523,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ridgid 18V</t>
+          <t>Makita LXT 18V</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5535,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Craftsman V20</t>
+          <t>Makita XGT 40V</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5547,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Worx 20V</t>
+          <t>Bosch 18V</t>
         </is>
       </c>
     </row>
@@ -5307,55 +5559,55 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Ryobi ONE+ 18V</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Acme Tools</t>
+          <t>Ridgid 18V</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Craftsman V20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Worx 20V</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lowe’s</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5619,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Acme Tools</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5631,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ace Hardware</t>
+          <t>Best Buy</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5643,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Harbor Freight</t>
+          <t>eBay</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5655,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Northern Tool</t>
+          <t>Home Depot</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5667,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Lowe’s</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5679,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5691,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Temu</t>
+          <t>Ace Hardware</t>
         </is>
       </c>
     </row>
@@ -5450,6 +5702,66 @@
         </is>
       </c>
       <c r="B87" t="inlineStr">
+        <is>
+          <t>Harbor Freight</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Northern Tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Grainger</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Temu</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>Other</t>
         </is>

--- a/tools.xlsx
+++ b/tools.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T66"/>
+  <dimension ref="A1:T69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>24" Snow Blower</t>
+          <t>24" 2 Stage Snow Blower</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4496,6 +4496,198 @@
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>77AC5E4D</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>DeWalt</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2100 PSI Pressure Washer</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pressure Washer</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Corded electric</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>110v</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>329</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>photos/77AC5E4D.png</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>C5333C39</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Worx</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Compact Circular Saw</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Circular Saw</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Corded electric</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>110v</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2017-06-13</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>60</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>photos/C5333C39.png</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>A20B115B</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ego</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>21" Single Stage Snow Blower</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Snow Blower</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>56V</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Ego 56V</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="n">
+        <v>700</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Lowe’s</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>photos/A20B115B.png</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4660,7 +4852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B92"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5199,7 +5391,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ratchet</t>
+          <t>Pressure Washer</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5403,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Router</t>
+          <t>Ratchet</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5415,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sander</t>
+          <t>Router</t>
         </is>
       </c>
     </row>
@@ -5235,7 +5427,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Scroll Saw</t>
+          <t>Sander</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5439,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shop Vac</t>
+          <t>Scroll Saw</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5451,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Snow Blower</t>
+          <t>Shop Vac</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5463,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stapler</t>
+          <t>Snow Blower</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5475,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Table Saw</t>
+          <t>Stapler</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5487,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Track Saw</t>
+          <t>Table Saw</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5499,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Trimmer</t>
+          <t>Track Saw</t>
         </is>
       </c>
     </row>
@@ -5319,19 +5511,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Trimmer</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Voltage</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5535,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>18V</t>
+          <t>12V</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5547,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>20V</t>
+          <t>18V</t>
         </is>
       </c>
     </row>
@@ -5367,7 +5559,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>24V</t>
+          <t>20V</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5571,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>36V</t>
+          <t>24V</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5583,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>40V</t>
+          <t>36V</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5595,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>56V</t>
+          <t>40V</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5607,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>60V</t>
+          <t>56V</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5619,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>120V</t>
+          <t>60V</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5631,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>120V / 240V</t>
+          <t>120V</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5643,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Corded / N/A</t>
+          <t>120V / 240V</t>
         </is>
       </c>
     </row>
@@ -5463,19 +5655,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Corded / N/A</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Battery platform</t>
+          <t>Voltage</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DeWalt 20V MAX</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5679,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ego 56V</t>
+          <t>DeWalt 20V MAX</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5691,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Milwaukee M18</t>
+          <t>Ego 56V</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5703,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Milwaukee M12</t>
+          <t>Milwaukee M18</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5715,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Makita LXT 18V</t>
+          <t>Milwaukee M12</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5727,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Makita XGT 40V</t>
+          <t>Makita LXT 18V</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5739,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bosch 18V</t>
+          <t>Makita XGT 40V</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5751,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ryobi ONE+ 18V</t>
+          <t>Bosch 18V</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5763,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ridgid 18V</t>
+          <t>Ryobi ONE+ 18V</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5775,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Craftsman V20</t>
+          <t>Ridgid 18V</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5787,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Worx 20V</t>
+          <t>Craftsman V20</t>
         </is>
       </c>
     </row>
@@ -5607,19 +5799,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Worx 20V</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Vendor</t>
+          <t>Battery platform</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Acme Tools</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5823,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Acme Tools</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5835,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Best Buy</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5847,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>eBay</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5859,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Lowe’s</t>
+          <t>Home Depot</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5871,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Lowe’s</t>
         </is>
       </c>
     </row>
@@ -5691,7 +5883,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ace Hardware</t>
+          <t>Amazon</t>
         </is>
       </c>
     </row>
@@ -5703,7 +5895,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Harbor Freight</t>
+          <t>Ace Hardware</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5907,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Northern Tool</t>
+          <t>Harbor Freight</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5919,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Northern Tool</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5931,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Walmart</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5943,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Temu</t>
+          <t>Grainger</t>
         </is>
       </c>
     </row>
@@ -5762,6 +5954,18 @@
         </is>
       </c>
       <c r="B92" t="inlineStr">
+        <is>
+          <t>Temu</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
         <is>
           <t>Other</t>
         </is>

--- a/tools.xlsx
+++ b/tools.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:T70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,7 +539,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nail Gun</t>
+          <t>Drill</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Brad Nailer</t>
+          <t>Nail Gun</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Brad Nailer</t>
+          <t>Nail Gun</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Impact Driver</t>
+          <t>Drill</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4688,6 +4688,70 @@
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>5E134FD7</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Ridgid</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Cordless Angle Grinder</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Grinder</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>18v</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ridgid 18V</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="n">
+        <v>89</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>photos/5E134FD7.png</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
